--- a/lab_5/models/metrics/et.xlsx
+++ b/lab_5/models/metrics/et.xlsx
@@ -467,163 +467,163 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7402</v>
+        <v>0.7541</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7793</v>
+        <v>0.7789</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7219</v>
+        <v>0.6952</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1542</v>
+        <v>0.157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2541</v>
+        <v>0.2561</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1702</v>
+        <v>0.1741</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2456</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7352</v>
+        <v>0.7175</v>
       </c>
       <c r="B3" t="n">
-        <v>0.76</v>
+        <v>0.7762</v>
       </c>
       <c r="C3" t="n">
-        <v>0.64</v>
+        <v>0.6415</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1383</v>
+        <v>0.1315</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2275</v>
+        <v>0.2183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1415</v>
+        <v>0.1295</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2027</v>
+        <v>0.1908</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.734</v>
+        <v>0.7557</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7826</v>
+        <v>0.7699</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7</v>
+        <v>0.6381</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1469</v>
+        <v>0.1489</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2428</v>
+        <v>0.2414</v>
       </c>
       <c r="F4" t="n">
-        <v>0.158</v>
+        <v>0.1583</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2298</v>
+        <v>0.2186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.7315</v>
+        <v>0.7417</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7489</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6533</v>
+        <v>0.6381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1386</v>
+        <v>0.1414</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2287</v>
+        <v>0.2314</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1425</v>
+        <v>0.1462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2061</v>
+        <v>0.2071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.7323</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7618</v>
+        <v>0.8154</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6755</v>
+        <v>0.7429</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1433</v>
+        <v>0.167</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2364</v>
+        <v>0.2727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1504</v>
+        <v>0.1924</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2178</v>
+        <v>0.2704</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.7346</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7665</v>
+        <v>0.7753</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6781</v>
+        <v>0.6712</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1442</v>
+        <v>0.1492</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2379</v>
+        <v>0.244</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1525</v>
+        <v>0.1601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2204</v>
+        <v>0.2262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.003</v>
+        <v>0.0151</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0126</v>
+        <v>0.0252</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0299</v>
+        <v>0.0419</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0059</v>
+        <v>0.0123</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0098</v>
+        <v>0.019</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0107</v>
+        <v>0.0218</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0158</v>
+        <v>0.0281</v>
       </c>
     </row>
   </sheetData>
